--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ILLINOIS_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ILLINOIS_2011.xlsx
@@ -409,7 +409,7 @@
         <v>62</v>
       </c>
       <c r="D3">
-        <v>0.000993319127802</v>
+        <v>0.0009933191278020002</v>
       </c>
     </row>
     <row r="4">
@@ -4117,7 +4117,7 @@
         <v>608</v>
       </c>
       <c r="D209">
-        <v>0.009740935962959</v>
+        <v>0.009740935962959002</v>
       </c>
     </row>
     <row r="210">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C218">
@@ -12397,7 +12397,7 @@
         <v>57</v>
       </c>
       <c r="D669">
-        <v>0.000913212746527</v>
+        <v>0.0009132127465270002</v>
       </c>
     </row>
     <row r="670">
@@ -12685,7 +12685,7 @@
         <v>57</v>
       </c>
       <c r="D685">
-        <v>0.000913212746527</v>
+        <v>0.0009132127465270002</v>
       </c>
     </row>
     <row r="686">
@@ -14575,7 +14575,7 @@
         <v>57</v>
       </c>
       <c r="D790">
-        <v>0.000913212746527</v>
+        <v>0.0009132127465270002</v>
       </c>
     </row>
     <row r="791">
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C804">
@@ -17250,7 +17250,7 @@
       </c>
       <c r="B939" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C939">
@@ -23323,7 +23323,7 @@
         <v>62</v>
       </c>
       <c r="D1276">
-        <v>0.000993319127802</v>
+        <v>0.0009933191278020002</v>
       </c>
     </row>
     <row r="1277">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="B1346" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1346">
@@ -25188,7 +25188,7 @@
       </c>
       <c r="B1380" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1380">
@@ -27780,7 +27780,7 @@
       </c>
       <c r="B1524" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1524">
